--- a/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
   <si>
     <t>LLYV.A</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,60 +656,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -737,8 +740,11 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -766,8 +772,11 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -795,8 +804,11 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -808,8 +820,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -837,8 +850,11 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -866,8 +882,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -880,23 +899,26 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>-2000</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -924,8 +946,11 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -934,66 +959,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2000</v>
       </c>
       <c r="F17" s="3">
         <v>2000</v>
       </c>
       <c r="G17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H17" s="3">
         <v>6000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5000</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-2000</v>
       </c>
       <c r="F18" s="3">
         <v>-2000</v>
       </c>
       <c r="G18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-6000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5000</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1005,153 +1037,169 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-31000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-179000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>84000</v>
       </c>
-      <c r="G20" s="3">
-        <v>144000</v>
-      </c>
       <c r="H20" s="3">
+        <v>142000</v>
+      </c>
+      <c r="I20" s="3">
         <v>17000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>16000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>411000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="E21" s="3">
         <v>28000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>177000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-86000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-150000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-22000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-411000</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E22" s="3">
         <v>8000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>7000</v>
       </c>
       <c r="F22" s="3">
         <v>7000</v>
       </c>
       <c r="G22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H22" s="3">
         <v>8000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2000</v>
       </c>
       <c r="I22" s="3">
         <v>2000</v>
       </c>
       <c r="J22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K22" s="3">
         <v>4000</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-138000</v>
+      </c>
+      <c r="E23" s="3">
         <v>20000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>170000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-93000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-156000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-415000</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E24" s="3">
         <v>5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>36000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-20000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-33000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-89000</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1179,66 +1227,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-109000</v>
+      </c>
+      <c r="E26" s="3">
         <v>15000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>134000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-73000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-123000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-326000</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-107000</v>
+      </c>
+      <c r="E27" s="3">
         <v>15000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>134000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-73000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-123000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-307000</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1266,8 +1323,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1295,8 +1355,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1324,8 +1387,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1353,66 +1419,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E32" s="3">
         <v>31000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>179000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-84000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-144000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-17000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-16000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-411000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-107000</v>
+      </c>
+      <c r="E33" s="3">
         <v>15000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>134000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-73000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-123000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-307000</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1440,71 +1515,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-107000</v>
+      </c>
+      <c r="E35" s="3">
         <v>15000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>134000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-73000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-123000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-307000</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1516,8 +1600,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1529,37 +1614,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>325000</v>
+      </c>
+      <c r="E41" s="3">
         <v>388000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>406000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>298000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>305000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>315000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1587,8 +1676,11 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1616,8 +1708,11 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1645,8 +1740,11 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1674,66 +1772,75 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>325000</v>
+      </c>
+      <c r="E46" s="3">
         <v>388000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>406000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>298000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>305000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>315000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>458000</v>
+      </c>
+      <c r="E47" s="3">
         <v>448000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>345000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>316000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>333000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>397000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>181000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>115000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1761,8 +1868,11 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1787,11 +1897,14 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1819,8 +1932,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1848,37 +1964,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>223000</v>
+      </c>
+      <c r="E52" s="3">
         <v>419000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>249000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>375000</v>
       </c>
-      <c r="G52" s="3">
-        <v>524000</v>
-      </c>
       <c r="H52" s="3">
+        <v>357000</v>
+      </c>
+      <c r="I52" s="3">
         <v>479000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>486000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>549000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1906,37 +2028,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1223000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1255000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1000000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>989000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1162000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1191000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>667000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>664000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1948,8 +2076,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1961,13 +2090,14 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>3000</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>3</v>
@@ -1975,153 +2105,168 @@
       <c r="F57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G57" s="3">
-        <v>1000</v>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="I57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>55000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>67000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>74000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>70000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>65000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>644000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>6000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14000</v>
       </c>
-      <c r="G59" s="3">
-        <v>9000</v>
-      </c>
       <c r="H59" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E60" s="3">
         <v>55000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>73000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>88000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>80000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>69000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>645000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1556000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1382000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1236000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1344000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1247000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1161000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>920000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1332000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
         <v>1000</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="E62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1000</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2135,8 +2280,11 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2164,8 +2312,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2193,8 +2344,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2222,37 +2376,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1560000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1438000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1147000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1248000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1327000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1230000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>920000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1977000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2264,8 +2424,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2293,8 +2454,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2322,8 +2486,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2351,8 +2518,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2380,8 +2550,11 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2409,8 +2582,11 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2438,8 +2614,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2467,8 +2646,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2496,37 +2678,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-359000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-206000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-170000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-282000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-188000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-62000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-278000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1338000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2554,71 +2742,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-107000</v>
+      </c>
+      <c r="E81" s="3">
         <v>15000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>134000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-73000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-123000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-307000</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2630,8 +2827,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2659,8 +2857,11 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2688,8 +2889,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2717,8 +2921,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2746,8 +2953,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2775,8 +2985,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2804,37 +3017,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2846,8 +3065,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2875,8 +3095,11 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2904,8 +3127,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2933,37 +3159,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>108000</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-9000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2975,8 +3207,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3004,8 +3237,11 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3033,8 +3269,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3062,8 +3301,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3091,37 +3333,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2000</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>11000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3149,26 +3397,29 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>108000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -3176,6 +3427,9 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>LLYV.A</t>
   </si>
@@ -656,63 +656,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -743,8 +747,11 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -775,8 +782,11 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -807,8 +817,11 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -821,8 +834,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -853,8 +867,11 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,8 +902,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -908,17 +928,20 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -949,8 +972,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -960,8 +986,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -969,31 +996,34 @@
         <v>4000</v>
       </c>
       <c r="E17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2000</v>
       </c>
       <c r="G17" s="3">
         <v>2000</v>
       </c>
       <c r="H17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I17" s="3">
         <v>6000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5000</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1001,31 +1031,34 @@
         <v>-4000</v>
       </c>
       <c r="E18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-2000</v>
       </c>
       <c r="G18" s="3">
         <v>-2000</v>
       </c>
       <c r="H18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-6000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5000</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1038,72 +1071,79 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E20" s="3">
         <v>127000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-31000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-179000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>84000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>142000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>17000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>16000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>411000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-131000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>28000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>177000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-86000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-148000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-22000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-411000</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1111,95 +1151,104 @@
         <v>7000</v>
       </c>
       <c r="E22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F22" s="3">
         <v>8000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>7000</v>
       </c>
       <c r="G22" s="3">
         <v>7000</v>
       </c>
       <c r="H22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I22" s="3">
         <v>8000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2000</v>
       </c>
       <c r="J22" s="3">
         <v>2000</v>
       </c>
       <c r="K22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L22" s="3">
         <v>4000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-138000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>20000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>170000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-93000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-156000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-415000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-29000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>36000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-20000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-33000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-89000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1230,72 +1279,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-109000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>134000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-73000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-123000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-326000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-107000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>134000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-73000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-123000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-307000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1326,8 +1384,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1358,8 +1419,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1390,8 +1454,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1422,72 +1489,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-127000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>31000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>179000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-84000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-142000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-17000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-16000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-411000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-107000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>134000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-73000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-123000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-307000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1518,77 +1594,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-107000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>134000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-73000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-123000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-307000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1601,8 +1686,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1615,40 +1701,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>314000</v>
+      </c>
+      <c r="E41" s="3">
         <v>325000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>388000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>406000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>298000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>305000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>315000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1679,13 +1769,16 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>1000</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -1711,8 +1804,11 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1743,8 +1839,11 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1775,72 +1874,81 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>315000</v>
+      </c>
+      <c r="E46" s="3">
         <v>325000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>388000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>406000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>298000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>305000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>315000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E47" s="3">
         <v>458000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>448000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>345000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>316000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>333000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>397000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>181000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>115000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1871,8 +1979,11 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1900,11 +2011,14 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1935,8 +2049,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1967,40 +2084,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E52" s="3">
         <v>223000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>419000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>249000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>375000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>357000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>479000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>486000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>549000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2031,40 +2154,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1231000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1223000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1255000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1000000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>989000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1162000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1191000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>667000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>664000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2077,8 +2206,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2091,40 +2221,44 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="3">
-        <v>2000</v>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="J57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2132,31 +2266,34 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>55000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>67000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>74000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>70000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>65000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>644000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2166,93 +2303,102 @@
       <c r="E59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
         <v>6000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3">
         <v>3000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>73000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>88000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>80000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>69000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
         <v>645000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1582000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1556000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1382000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1236000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1344000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1247000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1161000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>920000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1332000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2262,14 +2408,14 @@
       <c r="E62" s="3">
         <v>1000</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1000</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2283,8 +2429,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2315,8 +2464,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2347,8 +2499,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2379,40 +2534,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1583000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1560000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1438000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1147000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1248000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1327000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1230000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>920000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1977000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2425,8 +2586,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2457,8 +2619,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2489,8 +2654,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2521,8 +2689,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2553,8 +2724,11 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2585,8 +2759,11 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2617,8 +2794,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2649,8 +2829,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2681,40 +2864,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-359000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-206000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-170000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-282000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-188000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-62000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-278000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1338000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2745,77 +2934,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-107000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>134000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-73000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-123000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-307000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2828,8 +3026,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2860,8 +3059,11 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2892,8 +3094,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2924,8 +3129,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2956,8 +3164,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2988,8 +3199,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3020,40 +3234,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>-2000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3066,8 +3286,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3098,8 +3319,11 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3130,8 +3354,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3162,40 +3389,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>108000</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-9000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3208,8 +3441,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3240,8 +3474,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3272,8 +3509,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3304,8 +3544,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3336,40 +3579,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>-60000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2000</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>11000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3400,29 +3649,32 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-63000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>108000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -3430,6 +3682,9 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>LLYV.A</t>
   </si>
@@ -656,67 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -750,8 +754,11 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,8 +792,11 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,8 +830,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,8 +848,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,8 +884,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,8 +922,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -931,17 +951,20 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-1000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -975,8 +998,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,78 +1013,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
         <v>4000</v>
       </c>
-      <c r="E17" s="3">
-        <v>4000</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2000</v>
       </c>
       <c r="H17" s="3">
         <v>2000</v>
       </c>
       <c r="I17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4000</v>
       </c>
-      <c r="E18" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2000</v>
       </c>
       <c r="H18" s="3">
         <v>-2000</v>
       </c>
       <c r="I18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-6000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,183 +1105,199 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>11000</v>
-      </c>
-      <c r="E20" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>127000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-31000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-179000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>84000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>142000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>17000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>16000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>411000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-15000</v>
+        <v>-219000</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-131000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>177000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-86000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-148000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-22000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-16000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-411000</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
         <v>7000</v>
       </c>
-      <c r="E22" s="3">
-        <v>7000</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>7000</v>
       </c>
       <c r="H22" s="3">
         <v>7000</v>
       </c>
       <c r="I22" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J22" s="3">
         <v>8000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2000</v>
       </c>
       <c r="K22" s="3">
         <v>2000</v>
       </c>
       <c r="L22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M22" s="3">
         <v>4000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="E23" s="3">
+        <v>-227000</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
         <v>-138000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>170000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-93000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-156000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-415000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="K24" s="3">
         <v>-5000</v>
       </c>
-      <c r="E24" s="3">
-        <v>-29000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>36000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-33000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-89000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,78 +1331,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="E26" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
         <v>-109000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>134000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-73000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-123000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-326000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="E27" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>-107000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>134000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-73000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-123000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-307000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1445,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1483,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1521,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,78 +1559,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="E32" s="3">
+        <v>-212000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-127000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>31000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>179000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-84000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-142000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-17000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-16000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-411000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="E33" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>-107000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>134000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-73000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-123000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-307000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,83 +1673,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="E35" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>-107000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>134000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-73000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-123000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-307000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1772,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,43 +1788,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>314000</v>
-      </c>
-      <c r="E41" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3">
         <v>325000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>388000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>406000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>298000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>305000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>315000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1772,8 +1862,11 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1807,8 +1900,11 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1842,8 +1938,11 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1877,78 +1976,87 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>309000</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3">
+        <v>325000</v>
+      </c>
+      <c r="G46" s="3">
+        <v>388000</v>
+      </c>
+      <c r="H46" s="3">
+        <v>406000</v>
+      </c>
+      <c r="I46" s="3">
+        <v>298000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>305000</v>
+      </c>
+      <c r="K46" s="3">
         <v>315000</v>
       </c>
-      <c r="E46" s="3">
-        <v>325000</v>
-      </c>
-      <c r="F46" s="3">
-        <v>388000</v>
-      </c>
-      <c r="G46" s="3">
-        <v>406000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>298000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>305000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>315000</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>479000</v>
-      </c>
-      <c r="E47" s="3">
+        <v>589000</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>458000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>448000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>345000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>316000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>333000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>397000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>181000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>115000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1982,16 +2090,19 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
         <v>0</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2014,11 +2125,14 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2166,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,43 +2204,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>217000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>223000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>419000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>249000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>375000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>357000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>479000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>486000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>549000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,43 +2280,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1231000</v>
-      </c>
-      <c r="E54" s="3">
+        <v>1371000</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3">
         <v>1223000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1255000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1000000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>989000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1162000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1191000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>667000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>664000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2336,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,78 +2352,85 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I57" s="3">
-        <v>2000</v>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="K57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
+        <v>1769000</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>55000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>67000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>74000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>70000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>65000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>644000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2306,119 +2443,128 @@
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>6000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3">
+        <v>1770000</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3">
         <v>3000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>73000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>88000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>80000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>69000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
         <v>645000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1582000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>1556000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1382000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1236000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1344000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1247000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1161000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>920000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1332000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1000</v>
+        <v>90000</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1000</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2432,8 +2578,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2616,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2654,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,43 +2692,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1583000</v>
-      </c>
-      <c r="E66" s="3">
+        <v>1860000</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3">
         <v>1560000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1438000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1147000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1248000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1327000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1230000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>920000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1977000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2748,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2784,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2822,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +2860,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,8 +2898,11 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2762,8 +2936,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +2974,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3012,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,43 +3050,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-374000</v>
-      </c>
-      <c r="E76" s="3">
+        <v>-511000</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3">
         <v>-359000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-206000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-170000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-282000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-188000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-62000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-278000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1338000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,83 +3126,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="E81" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>-107000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>134000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-73000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-123000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-307000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,8 +3225,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3062,8 +3261,11 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3299,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3337,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3375,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3413,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3451,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="H89" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="J89" s="3">
         <v>-10000</v>
       </c>
-      <c r="E89" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="M89" s="3">
         <v>-4000</v>
       </c>
-      <c r="G89" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,8 +3507,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3322,8 +3543,11 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3581,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,43 +3619,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-3000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>108000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-9000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,8 +3675,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3477,8 +3711,11 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3749,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +3787,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,43 +3825,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>-60000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2000</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>11000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3652,32 +3901,35 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-11000</v>
+        <v>-6000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-63000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>108000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
@@ -3685,6 +3937,9 @@
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>LLYV.A</t>
   </si>
@@ -656,97 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45382</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45291</v>
       </c>
       <c r="K7" s="2">
         <v>45291</v>
       </c>
       <c r="L7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>61700</v>
+      </c>
+      <c r="F8" s="3">
+        <v>185700</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>104300</v>
+      </c>
+      <c r="I8" s="3">
+        <v>64200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>172000</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -763,31 +766,34 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>107400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>49000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>152000</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>90300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>55700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>147200</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -804,31 +810,34 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>33700</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>14000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>24900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -845,8 +854,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,8 +916,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,13 +960,16 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>1200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -961,14 +980,14 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>61200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>800</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -976,40 +995,43 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-1000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>13100</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1026,8 +1048,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,90 +1065,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9000</v>
+        <v>149600</v>
       </c>
       <c r="E17" s="3">
-        <v>7000</v>
+        <v>78500</v>
       </c>
       <c r="F17" s="3">
+        <v>201600</v>
+      </c>
+      <c r="G17" s="3">
         <v>4000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3000</v>
-      </c>
       <c r="H17" s="3">
-        <v>2000</v>
+        <v>118800</v>
       </c>
       <c r="I17" s="3">
-        <v>2000</v>
+        <v>78600</v>
       </c>
       <c r="J17" s="3">
-        <v>6000</v>
+        <v>189500</v>
       </c>
       <c r="K17" s="3">
         <v>6000</v>
       </c>
       <c r="L17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M17" s="3">
         <v>5000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-9000</v>
+        <v>-15000</v>
       </c>
       <c r="E18" s="3">
-        <v>-7000</v>
+        <v>-16800</v>
       </c>
       <c r="F18" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-4000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3000</v>
-      </c>
       <c r="H18" s="3">
-        <v>-2000</v>
+        <v>-14500</v>
       </c>
       <c r="I18" s="3">
-        <v>-2000</v>
+        <v>-14400</v>
       </c>
       <c r="J18" s="3">
-        <v>-6000</v>
+        <v>-17500</v>
       </c>
       <c r="K18" s="3">
         <v>-6000</v>
       </c>
       <c r="L18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="M18" s="3">
         <v>-5000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,213 +1171,229 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>50000</v>
+        <v>-251400</v>
       </c>
       <c r="E20" s="3">
-        <v>212000</v>
+        <v>51200</v>
       </c>
       <c r="F20" s="3">
-        <v>127000</v>
+        <v>222700</v>
       </c>
       <c r="G20" s="3">
-        <v>-31000</v>
+        <v>11000</v>
       </c>
       <c r="H20" s="3">
-        <v>-179000</v>
+        <v>138200</v>
       </c>
       <c r="I20" s="3">
-        <v>84000</v>
+        <v>-35500</v>
       </c>
       <c r="J20" s="3">
-        <v>142000</v>
+        <v>-160300</v>
       </c>
       <c r="K20" s="3">
         <v>142000</v>
       </c>
       <c r="L20" s="3">
+        <v>142000</v>
+      </c>
+      <c r="M20" s="3">
         <v>17000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>411000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-59000</v>
+        <v>243000</v>
       </c>
       <c r="E21" s="3">
-        <v>-219000</v>
+        <v>-61500</v>
       </c>
       <c r="F21" s="3">
-        <v>-131000</v>
+        <v>-225600</v>
       </c>
       <c r="G21" s="3">
-        <v>28000</v>
+        <v>-15000</v>
       </c>
       <c r="H21" s="3">
-        <v>177000</v>
+        <v>-146200</v>
       </c>
       <c r="I21" s="3">
-        <v>-86000</v>
+        <v>28100</v>
       </c>
       <c r="J21" s="3">
-        <v>-148000</v>
+        <v>156800</v>
       </c>
       <c r="K21" s="3">
         <v>-148000</v>
       </c>
       <c r="L21" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="M21" s="3">
         <v>-22000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-411000</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F22" s="3">
+        <v>7800</v>
+      </c>
+      <c r="G22" s="3">
         <v>7000</v>
       </c>
-      <c r="E22" s="3">
-        <v>8000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>7000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>8000</v>
-      </c>
       <c r="H22" s="3">
-        <v>7000</v>
+        <v>7300</v>
       </c>
       <c r="I22" s="3">
-        <v>7000</v>
+        <v>7400</v>
       </c>
       <c r="J22" s="3">
-        <v>8000</v>
+        <v>7300</v>
       </c>
       <c r="K22" s="3">
         <v>8000</v>
       </c>
       <c r="L22" s="3">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="M22" s="3">
         <v>2000</v>
       </c>
       <c r="N22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O22" s="3">
         <v>4000</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-66000</v>
+        <v>231000</v>
       </c>
       <c r="E23" s="3">
-        <v>-227000</v>
+        <v>-71300</v>
       </c>
       <c r="F23" s="3">
-        <v>-138000</v>
+        <v>-237900</v>
       </c>
       <c r="G23" s="3">
-        <v>20000</v>
+        <v>-22000</v>
       </c>
       <c r="H23" s="3">
-        <v>170000</v>
+        <v>-216400</v>
       </c>
       <c r="I23" s="3">
-        <v>-93000</v>
+        <v>19400</v>
       </c>
       <c r="J23" s="3">
-        <v>-156000</v>
+        <v>145800</v>
       </c>
       <c r="K23" s="3">
         <v>-156000</v>
       </c>
       <c r="L23" s="3">
+        <v>-156000</v>
+      </c>
+      <c r="M23" s="3">
         <v>-24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-415000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-13000</v>
+        <v>52600</v>
       </c>
       <c r="E24" s="3">
-        <v>-49000</v>
+        <v>-15600</v>
       </c>
       <c r="F24" s="3">
-        <v>-29000</v>
+        <v>-45100</v>
       </c>
       <c r="G24" s="3">
-        <v>5000</v>
+        <v>-5000</v>
       </c>
       <c r="H24" s="3">
-        <v>36000</v>
+        <v>-45600</v>
       </c>
       <c r="I24" s="3">
-        <v>-20000</v>
+        <v>4200</v>
       </c>
       <c r="J24" s="3">
-        <v>-33000</v>
+        <v>31400</v>
       </c>
       <c r="K24" s="3">
         <v>-33000</v>
       </c>
       <c r="L24" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="M24" s="3">
         <v>-5000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-89000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,90 +1433,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-53000</v>
+        <v>178400</v>
       </c>
       <c r="E26" s="3">
-        <v>-178000</v>
+        <v>-55700</v>
       </c>
       <c r="F26" s="3">
-        <v>-109000</v>
+        <v>-192800</v>
       </c>
       <c r="G26" s="3">
-        <v>15000</v>
+        <v>-17000</v>
       </c>
       <c r="H26" s="3">
-        <v>134000</v>
+        <v>-170700</v>
       </c>
       <c r="I26" s="3">
-        <v>-73000</v>
+        <v>15300</v>
       </c>
       <c r="J26" s="3">
-        <v>-123000</v>
+        <v>114300</v>
       </c>
       <c r="K26" s="3">
         <v>-123000</v>
       </c>
       <c r="L26" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="M26" s="3">
         <v>-19000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-326000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-53000</v>
+        <v>178600</v>
       </c>
       <c r="E27" s="3">
-        <v>-178000</v>
+        <v>-55700</v>
       </c>
       <c r="F27" s="3">
-        <v>-107000</v>
+        <v>-192800</v>
       </c>
       <c r="G27" s="3">
-        <v>15000</v>
+        <v>-17000</v>
       </c>
       <c r="H27" s="3">
-        <v>134000</v>
+        <v>-169400</v>
       </c>
       <c r="I27" s="3">
-        <v>-73000</v>
+        <v>15300</v>
       </c>
       <c r="J27" s="3">
-        <v>-123000</v>
+        <v>114400</v>
       </c>
       <c r="K27" s="3">
         <v>-123000</v>
       </c>
       <c r="L27" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="M27" s="3">
         <v>-19000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-307000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1565,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1609,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1653,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,90 +1697,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-50000</v>
+        <v>251400</v>
       </c>
       <c r="E32" s="3">
-        <v>-212000</v>
+        <v>-51200</v>
       </c>
       <c r="F32" s="3">
-        <v>-127000</v>
+        <v>-222700</v>
       </c>
       <c r="G32" s="3">
-        <v>31000</v>
+        <v>-11000</v>
       </c>
       <c r="H32" s="3">
-        <v>179000</v>
+        <v>-138200</v>
       </c>
       <c r="I32" s="3">
-        <v>-84000</v>
+        <v>35500</v>
       </c>
       <c r="J32" s="3">
-        <v>-142000</v>
+        <v>160300</v>
       </c>
       <c r="K32" s="3">
         <v>-142000</v>
       </c>
       <c r="L32" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="M32" s="3">
         <v>-17000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-411000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-53000</v>
+        <v>178600</v>
       </c>
       <c r="E33" s="3">
-        <v>-178000</v>
+        <v>-55700</v>
       </c>
       <c r="F33" s="3">
-        <v>-107000</v>
+        <v>-192800</v>
       </c>
       <c r="G33" s="3">
-        <v>15000</v>
+        <v>-17000</v>
       </c>
       <c r="H33" s="3">
-        <v>134000</v>
+        <v>-169400</v>
       </c>
       <c r="I33" s="3">
-        <v>-73000</v>
+        <v>15300</v>
       </c>
       <c r="J33" s="3">
-        <v>-123000</v>
+        <v>114400</v>
       </c>
       <c r="K33" s="3">
         <v>-123000</v>
       </c>
       <c r="L33" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="M33" s="3">
         <v>-19000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-307000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,95 +1829,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-53000</v>
+        <v>178600</v>
       </c>
       <c r="E35" s="3">
-        <v>-178000</v>
+        <v>-55700</v>
       </c>
       <c r="F35" s="3">
-        <v>-107000</v>
+        <v>-192800</v>
       </c>
       <c r="G35" s="3">
-        <v>15000</v>
+        <v>-17000</v>
       </c>
       <c r="H35" s="3">
-        <v>134000</v>
+        <v>-169400</v>
       </c>
       <c r="I35" s="3">
-        <v>-73000</v>
+        <v>15300</v>
       </c>
       <c r="J35" s="3">
-        <v>-123000</v>
+        <v>114400</v>
       </c>
       <c r="K35" s="3">
         <v>-123000</v>
       </c>
       <c r="L35" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="M35" s="3">
         <v>-19000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-307000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45382</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45291</v>
       </c>
       <c r="K38" s="2">
         <v>45291</v>
       </c>
       <c r="L38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +1942,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,49 +1960,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>297000</v>
+        <v>545500</v>
       </c>
       <c r="E41" s="3">
-        <v>308000</v>
+        <v>375800</v>
       </c>
       <c r="F41" s="3">
-        <v>325000</v>
+        <v>378400</v>
       </c>
       <c r="G41" s="3">
+        <v>314000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>402600</v>
+      </c>
+      <c r="I41" s="3">
         <v>388000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>406000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>298000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>305000</v>
       </c>
       <c r="K41" s="3">
         <v>305000</v>
       </c>
       <c r="L41" s="3">
+        <v>305000</v>
+      </c>
+      <c r="M41" s="3">
         <v>315000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1957,25 +2046,28 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>36600</v>
+      </c>
+      <c r="F43" s="3">
+        <v>41400</v>
+      </c>
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>20100</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1998,8 +2090,11 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2039,25 +2134,28 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F45" s="3">
+        <v>7000</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>4700</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -2080,90 +2178,99 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>298000</v>
+        <v>629500</v>
       </c>
       <c r="E46" s="3">
-        <v>309000</v>
+        <v>483900</v>
       </c>
       <c r="F46" s="3">
-        <v>325000</v>
+        <v>470800</v>
       </c>
       <c r="G46" s="3">
+        <v>315000</v>
+      </c>
+      <c r="H46" s="3">
+        <v>472400</v>
+      </c>
+      <c r="I46" s="3">
         <v>388000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>406000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>298000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>305000</v>
       </c>
       <c r="K46" s="3">
         <v>305000</v>
       </c>
       <c r="L46" s="3">
+        <v>305000</v>
+      </c>
+      <c r="M46" s="3">
         <v>315000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>708000</v>
+        <v>786300</v>
       </c>
       <c r="E47" s="3">
-        <v>589000</v>
+        <v>847900</v>
       </c>
       <c r="F47" s="3">
-        <v>458000</v>
+        <v>727800</v>
       </c>
       <c r="G47" s="3">
+        <v>479000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>603800</v>
+      </c>
+      <c r="I47" s="3">
         <v>448000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>345000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>316000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>333000</v>
       </c>
       <c r="K47" s="3">
         <v>333000</v>
       </c>
       <c r="L47" s="3">
+        <v>333000</v>
+      </c>
+      <c r="M47" s="3">
         <v>397000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>181000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>115000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2203,25 +2310,28 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>246000</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>249900</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>256700</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>267300</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -2241,11 +2351,14 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2398,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,49 +2442,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>216000</v>
+        <v>43200</v>
       </c>
       <c r="E52" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G52" s="3">
         <v>217000</v>
       </c>
-      <c r="F52" s="3">
-        <v>223000</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I52" s="3">
         <v>419000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>249000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>375000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>357000</v>
       </c>
       <c r="K52" s="3">
         <v>357000</v>
       </c>
       <c r="L52" s="3">
+        <v>357000</v>
+      </c>
+      <c r="M52" s="3">
         <v>479000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>486000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>549000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,49 +2530,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1489000</v>
+        <v>1888900</v>
       </c>
       <c r="E54" s="3">
-        <v>1371000</v>
+        <v>1877800</v>
       </c>
       <c r="F54" s="3">
-        <v>1223000</v>
+        <v>1737100</v>
       </c>
       <c r="G54" s="3">
+        <v>1231000</v>
+      </c>
+      <c r="H54" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="I54" s="3">
         <v>1255000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1000000</v>
-      </c>
-      <c r="I54" s="3">
-        <v>989000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>1162000</v>
       </c>
       <c r="K54" s="3">
         <v>1162000</v>
       </c>
       <c r="L54" s="3">
+        <v>1162000</v>
+      </c>
+      <c r="M54" s="3">
         <v>1191000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>667000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>664000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2594,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,31 +2612,32 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="E57" s="3">
-        <v>1000</v>
+        <v>9600</v>
       </c>
       <c r="F57" s="3">
-        <v>3000</v>
+        <v>15200</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+      <c r="H57" s="3">
+        <v>16300</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J57" s="3">
-        <v>2000</v>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>2000</v>
@@ -2515,140 +2645,152 @@
       <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="M57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1873000</v>
+        <v>1666500</v>
       </c>
       <c r="E58" s="3">
+        <v>1872900</v>
+      </c>
+      <c r="F58" s="3">
         <v>1769000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>55000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>67000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>74000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>70000</v>
       </c>
       <c r="K58" s="3">
         <v>70000</v>
       </c>
       <c r="L58" s="3">
+        <v>70000</v>
+      </c>
+      <c r="M58" s="3">
         <v>65000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>644000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>194500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>171200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>136300</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H59" s="3">
+        <v>136600</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>6000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>14000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>8000</v>
       </c>
       <c r="K59" s="3">
         <v>8000</v>
       </c>
       <c r="L59" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M59" s="3">
         <v>2000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1873000</v>
+        <v>1896700</v>
       </c>
       <c r="E60" s="3">
-        <v>1770000</v>
+        <v>2095800</v>
       </c>
       <c r="F60" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G60" s="3">
+        <v>1965100</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
+        <v>187500</v>
+      </c>
+      <c r="I60" s="3">
         <v>55000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>73000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>88000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>80000</v>
       </c>
       <c r="K60" s="3">
         <v>80000</v>
       </c>
       <c r="L60" s="3">
+        <v>80000</v>
+      </c>
+      <c r="M60" s="3">
         <v>69000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3">
         <v>645000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2659,54 +2801,57 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>1556000</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>1582000</v>
+      </c>
+      <c r="H61" s="3">
+        <v>1556400</v>
+      </c>
+      <c r="I61" s="3">
         <v>1382000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1236000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1344000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1247000</v>
       </c>
       <c r="K61" s="3">
         <v>1247000</v>
       </c>
       <c r="L61" s="3">
+        <v>1247000</v>
+      </c>
+      <c r="M61" s="3">
         <v>1161000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>920000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1332000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>150000</v>
+        <v>19300</v>
       </c>
       <c r="E62" s="3">
-        <v>90000</v>
+        <v>169100</v>
       </c>
       <c r="F62" s="3">
-        <v>1000</v>
+        <v>110700</v>
       </c>
       <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>18300</v>
       </c>
       <c r="I62" s="3">
         <v>1000</v>
@@ -2729,8 +2874,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +2918,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +2962,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,49 +3006,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2023000</v>
+        <v>1916000</v>
       </c>
       <c r="E66" s="3">
-        <v>1860000</v>
+        <v>2264900</v>
       </c>
       <c r="F66" s="3">
-        <v>1560000</v>
+        <v>2075800</v>
       </c>
       <c r="G66" s="3">
+        <v>1583000</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1762100</v>
+      </c>
+      <c r="I66" s="3">
         <v>1438000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1147000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1248000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1327000</v>
       </c>
       <c r="K66" s="3">
         <v>1327000</v>
       </c>
       <c r="L66" s="3">
+        <v>1327000</v>
+      </c>
+      <c r="M66" s="3">
         <v>1230000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>920000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1977000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3070,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3112,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3156,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3033,8 +3200,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,25 +3244,28 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-437100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-633400</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-577700</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+      <c r="H72" s="3">
+        <v>-370000</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -3115,8 +3288,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3332,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3376,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,49 +3420,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-556000</v>
+        <v>-49100</v>
       </c>
       <c r="E76" s="3">
-        <v>-511000</v>
+        <v>-409200</v>
       </c>
       <c r="F76" s="3">
-        <v>-359000</v>
+        <v>-360900</v>
       </c>
       <c r="G76" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="H76" s="3">
+        <v>-199200</v>
+      </c>
+      <c r="I76" s="3">
         <v>-206000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-170000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-282000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-188000</v>
       </c>
       <c r="K76" s="3">
         <v>-188000</v>
       </c>
       <c r="L76" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="M76" s="3">
         <v>-62000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-278000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1338000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,95 +3508,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45382</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45291</v>
       </c>
       <c r="K80" s="2">
         <v>45291</v>
       </c>
       <c r="L80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-53000</v>
+        <v>178600</v>
       </c>
       <c r="E81" s="3">
-        <v>-178000</v>
+        <v>-55700</v>
       </c>
       <c r="F81" s="3">
-        <v>-107000</v>
+        <v>-192800</v>
       </c>
       <c r="G81" s="3">
-        <v>15000</v>
+        <v>-17000</v>
       </c>
       <c r="H81" s="3">
-        <v>134000</v>
+        <v>-169400</v>
       </c>
       <c r="I81" s="3">
-        <v>-73000</v>
+        <v>15300</v>
       </c>
       <c r="J81" s="3">
-        <v>-123000</v>
+        <v>114400</v>
       </c>
       <c r="K81" s="3">
         <v>-123000</v>
       </c>
       <c r="L81" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="M81" s="3">
         <v>-19000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-307000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,19 +3621,20 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>300</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -3465,8 +3663,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3707,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3751,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +3795,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +3839,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,49 +3883,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-12000</v>
+        <v>-600</v>
       </c>
       <c r="E89" s="3">
-        <v>-6000</v>
+        <v>-2100</v>
       </c>
       <c r="F89" s="3">
-        <v>-3000</v>
+        <v>-16800</v>
       </c>
       <c r="G89" s="3">
-        <v>-4000</v>
+        <v>-10000</v>
       </c>
       <c r="H89" s="3">
-        <v>2000</v>
+        <v>9900</v>
       </c>
       <c r="I89" s="3">
-        <v>-9000</v>
+        <v>5600</v>
       </c>
       <c r="J89" s="3">
-        <v>-10000</v>
+        <v>-31800</v>
       </c>
       <c r="K89" s="3">
         <v>-10000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="L89" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,8 +3947,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3769,8 +3989,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4033,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,49 +4077,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="G94" s="3">
-        <v>-3000</v>
+        <v>-1000</v>
       </c>
       <c r="H94" s="3">
-        <v>108000</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-100</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-97400</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-9000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,8 +4141,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3950,8 +4183,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4227,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4271,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,60 +4315,66 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+        <v>170000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-400</v>
       </c>
       <c r="F100" s="3">
-        <v>-60000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-11000</v>
+        <v>-1900</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
-        <v>-2000</v>
+        <v>-60100</v>
       </c>
       <c r="I100" s="3">
-        <v>2000</v>
+        <v>-17500</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>303400</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>11000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>16000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>500</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-100</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -4155,37 +4403,40 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>169700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-11000</v>
       </c>
-      <c r="E102" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-63000</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-18000</v>
-      </c>
       <c r="H102" s="3">
-        <v>108000</v>
+        <v>-51100</v>
       </c>
       <c r="I102" s="3">
-        <v>-7000</v>
+        <v>-11500</v>
       </c>
       <c r="J102" s="3">
-        <v>-10000</v>
+        <v>174100</v>
       </c>
       <c r="K102" s="3">
         <v>-10000</v>
       </c>
       <c r="L102" s="3">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -4194,6 +4445,9 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LLYV.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>LLYV.A</t>
   </si>
@@ -656,104 +656,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45291</v>
       </c>
       <c r="L7" s="2">
         <v>45291</v>
       </c>
       <c r="M7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>63600</v>
+      </c>
+      <c r="E8" s="3">
         <v>134600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>61700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>185700</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3">
+        <v>47100</v>
+      </c>
+      <c r="I8" s="3">
         <v>104300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>64200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>172000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -769,35 +773,38 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E9" s="3">
         <v>107400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>152000</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3">
+        <v>41500</v>
+      </c>
+      <c r="I9" s="3">
         <v>90300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>55700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>147200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -813,35 +820,38 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E10" s="3">
         <v>27100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>33700</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I10" s="3">
         <v>14000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -857,8 +867,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +888,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,8 +933,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,52 +980,58 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>1200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>61200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>-1000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1019,23 +1042,23 @@
         <v>6500</v>
       </c>
       <c r="F15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="G15" s="3">
         <v>13100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>6500</v>
       </c>
       <c r="I15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J15" s="3">
         <v>7000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1051,8 +1074,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1066,96 +1092,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E17" s="3">
         <v>149600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>78500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>201600</v>
       </c>
-      <c r="G17" s="3">
-        <v>4000</v>
-      </c>
       <c r="H17" s="3">
+        <v>64300</v>
+      </c>
+      <c r="I17" s="3">
         <v>118800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>78600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>189500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>6000</v>
       </c>
       <c r="L17" s="3">
         <v>6000</v>
       </c>
       <c r="M17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N17" s="3">
         <v>5000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-15000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-14500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-6000</v>
       </c>
       <c r="L18" s="3">
         <v>-6000</v>
       </c>
       <c r="M18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="N18" s="3">
         <v>-5000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1172,228 +1205,244 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>356000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-251400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>51200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>222700</v>
       </c>
-      <c r="G20" s="3">
-        <v>11000</v>
-      </c>
       <c r="H20" s="3">
+        <v>16700</v>
+      </c>
+      <c r="I20" s="3">
         <v>138200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-35500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-160300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>142000</v>
       </c>
       <c r="L20" s="3">
         <v>142000</v>
       </c>
       <c r="M20" s="3">
+        <v>142000</v>
+      </c>
+      <c r="N20" s="3">
         <v>17000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>411000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-366200</v>
+      </c>
+      <c r="E21" s="3">
         <v>243000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-61500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-225600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-15000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-146200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>28100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>156800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-148000</v>
       </c>
       <c r="L21" s="3">
         <v>-148000</v>
       </c>
       <c r="M21" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="N21" s="3">
         <v>-22000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-411000</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>7400</v>
+        <v>7600</v>
       </c>
       <c r="E22" s="3">
         <v>7400</v>
       </c>
       <c r="F22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G22" s="3">
         <v>7800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>7000</v>
       </c>
       <c r="H22" s="3">
         <v>7300</v>
       </c>
       <c r="I22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J22" s="3">
         <v>7400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>8000</v>
       </c>
       <c r="L22" s="3">
         <v>8000</v>
       </c>
       <c r="M22" s="3">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="N22" s="3">
         <v>2000</v>
       </c>
       <c r="O22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P22" s="3">
         <v>4000</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-375600</v>
+      </c>
+      <c r="E23" s="3">
         <v>231000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-71300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-237900</v>
       </c>
-      <c r="G23" s="3">
-        <v>-22000</v>
-      </c>
       <c r="H23" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-216400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>19400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>145800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-156000</v>
       </c>
       <c r="L23" s="3">
         <v>-156000</v>
       </c>
       <c r="M23" s="3">
+        <v>-156000</v>
+      </c>
+      <c r="N23" s="3">
         <v>-24000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-415000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-81500</v>
+      </c>
+      <c r="E24" s="3">
         <v>52600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-15600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-45100</v>
       </c>
-      <c r="G24" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H24" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="I24" s="3">
         <v>-45600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>31400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-33000</v>
       </c>
       <c r="L24" s="3">
         <v>-33000</v>
       </c>
       <c r="M24" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="N24" s="3">
         <v>-5000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-89000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1436,96 +1485,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-294100</v>
+      </c>
+      <c r="E26" s="3">
         <v>178400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-55700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-192800</v>
       </c>
-      <c r="G26" s="3">
-        <v>-17000</v>
-      </c>
       <c r="H26" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-170700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>114300</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-123000</v>
       </c>
       <c r="L26" s="3">
         <v>-123000</v>
       </c>
       <c r="M26" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="N26" s="3">
         <v>-19000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-326000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-294100</v>
+      </c>
+      <c r="E27" s="3">
         <v>178600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-55700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-192800</v>
       </c>
-      <c r="G27" s="3">
-        <v>-17000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-169400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>114400</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-123000</v>
       </c>
       <c r="L27" s="3">
         <v>-123000</v>
       </c>
       <c r="M27" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="N27" s="3">
         <v>-19000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-307000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1568,8 +1626,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1612,8 +1673,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1656,8 +1720,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1700,96 +1767,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-356000</v>
+      </c>
+      <c r="E32" s="3">
         <v>251400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-51200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-222700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-11000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-138200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>35500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>160300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-142000</v>
       </c>
       <c r="L32" s="3">
         <v>-142000</v>
       </c>
       <c r="M32" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="N32" s="3">
         <v>-17000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-411000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-294100</v>
+      </c>
+      <c r="E33" s="3">
         <v>178600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-55700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-192800</v>
       </c>
-      <c r="G33" s="3">
-        <v>-17000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="I33" s="3">
         <v>-169400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>114400</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-123000</v>
       </c>
       <c r="L33" s="3">
         <v>-123000</v>
       </c>
       <c r="M33" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="N33" s="3">
         <v>-19000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-307000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1832,101 +1908,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-294100</v>
+      </c>
+      <c r="E35" s="3">
         <v>178600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-55700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-192800</v>
       </c>
-      <c r="G35" s="3">
-        <v>-17000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="I35" s="3">
         <v>-169400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>114400</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-123000</v>
       </c>
       <c r="L35" s="3">
         <v>-123000</v>
       </c>
       <c r="M35" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="N35" s="3">
         <v>-19000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-307000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45291</v>
       </c>
       <c r="L38" s="2">
         <v>45291</v>
       </c>
       <c r="M38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1943,8 +2028,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1961,52 +2047,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>524400</v>
+      </c>
+      <c r="E41" s="3">
         <v>545500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>375800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>378400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>314000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>402600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>388000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>406000</v>
-      </c>
-      <c r="K41" s="3">
-        <v>305000</v>
       </c>
       <c r="L41" s="3">
         <v>305000</v>
       </c>
       <c r="M41" s="3">
+        <v>305000</v>
+      </c>
+      <c r="N41" s="3">
         <v>315000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2049,29 +2139,32 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E43" s="3">
         <v>30400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>36600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,8 +2186,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2137,29 +2233,32 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E45" s="3">
         <v>9400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>4700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,96 +2280,105 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>670200</v>
+      </c>
+      <c r="E46" s="3">
         <v>629500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>483900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>470800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>315000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>472400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>388000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>406000</v>
-      </c>
-      <c r="K46" s="3">
-        <v>305000</v>
       </c>
       <c r="L46" s="3">
         <v>305000</v>
       </c>
       <c r="M46" s="3">
+        <v>305000</v>
+      </c>
+      <c r="N46" s="3">
         <v>315000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>671900</v>
+      </c>
+      <c r="E47" s="3">
         <v>786300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>847900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>727800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>479000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>603800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>448000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>345000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>333000</v>
       </c>
       <c r="L47" s="3">
         <v>333000</v>
       </c>
       <c r="M47" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N47" s="3">
         <v>397000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>181000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>115000</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2313,29 +2421,32 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>239800</v>
+      </c>
+      <c r="E49" s="3">
         <v>246000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>249900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>256700</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>267300</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
@@ -2354,11 +2465,14 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2401,8 +2515,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2445,52 +2562,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E52" s="3">
         <v>43200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>217000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>419000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>249000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>357000</v>
       </c>
       <c r="L52" s="3">
         <v>357000</v>
       </c>
       <c r="M52" s="3">
+        <v>357000</v>
+      </c>
+      <c r="N52" s="3">
         <v>479000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>486000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>549000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2533,52 +2656,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1884100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1888900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1877800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1737100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1231000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1585000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1255000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1000000</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1162000</v>
       </c>
       <c r="L54" s="3">
         <v>1162000</v>
       </c>
       <c r="M54" s="3">
+        <v>1162000</v>
+      </c>
+      <c r="N54" s="3">
         <v>1191000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>667000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>664000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2595,8 +2724,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2613,34 +2743,35 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E57" s="3">
         <v>11500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15200</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>16300</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>2000</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L57" s="3">
         <v>2000</v>
@@ -2648,149 +2779,161 @@
       <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="N57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1818500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1666500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1872900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1769000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>55000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>67000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>70000</v>
       </c>
       <c r="L58" s="3">
         <v>70000</v>
       </c>
       <c r="M58" s="3">
+        <v>70000</v>
+      </c>
+      <c r="N58" s="3">
         <v>65000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>644000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>305900</v>
+      </c>
+      <c r="E59" s="3">
         <v>194500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>171200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>136300</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>136600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>6000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>8000</v>
       </c>
       <c r="L59" s="3">
         <v>8000</v>
       </c>
       <c r="M59" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N59" s="3">
         <v>2000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2160400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1896700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2095800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1965100</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3">
         <v>187500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>73000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>80000</v>
       </c>
       <c r="L60" s="3">
         <v>80000</v>
       </c>
       <c r="M60" s="3">
+        <v>80000</v>
+      </c>
+      <c r="N60" s="3">
         <v>69000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3">
         <v>645000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2804,61 +2947,64 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>1582000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1556400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1382000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1236000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1247000</v>
       </c>
       <c r="L61" s="3">
         <v>1247000</v>
       </c>
       <c r="M61" s="3">
+        <v>1247000</v>
+      </c>
+      <c r="N61" s="3">
         <v>1161000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>920000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1332000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E62" s="3">
         <v>19300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>169100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>110700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2877,8 +3023,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2921,8 +3070,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2965,8 +3117,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3009,52 +3164,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2179800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1916000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2264900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2075800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1583000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1762100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1438000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1147000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1327000</v>
       </c>
       <c r="L66" s="3">
         <v>1327000</v>
       </c>
       <c r="M66" s="3">
+        <v>1327000</v>
+      </c>
+      <c r="N66" s="3">
         <v>1230000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>920000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1977000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3071,8 +3232,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3115,8 +3277,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3159,8 +3324,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3203,8 +3371,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3247,29 +3418,32 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-731200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-437100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-633400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-577700</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>-370000</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3291,8 +3465,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3335,8 +3512,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3379,8 +3559,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3423,52 +3606,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-317700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-49100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-409200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-360900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-374000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-199200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-206000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-170000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>-188000</v>
       </c>
       <c r="L76" s="3">
         <v>-188000</v>
       </c>
       <c r="M76" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="N76" s="3">
         <v>-62000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-278000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1338000</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3511,101 +3700,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45291</v>
       </c>
       <c r="L80" s="2">
         <v>45291</v>
       </c>
       <c r="M80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-294100</v>
+      </c>
+      <c r="E81" s="3">
         <v>178600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-55700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-192800</v>
       </c>
-      <c r="G81" s="3">
-        <v>-17000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="I81" s="3">
         <v>-169400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>114400</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-123000</v>
       </c>
       <c r="L81" s="3">
         <v>-123000</v>
       </c>
       <c r="M81" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="N81" s="3">
         <v>-19000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-307000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3622,8 +3820,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3634,11 +3833,11 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3666,8 +3865,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3710,8 +3912,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3754,8 +3959,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3798,8 +4006,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3842,8 +4053,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3886,52 +4100,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16800</v>
       </c>
-      <c r="G89" s="3">
-        <v>-10000</v>
-      </c>
       <c r="H89" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="I89" s="3">
         <v>9900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-31800</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-10000</v>
       </c>
       <c r="L89" s="3">
         <v>-10000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="M89" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3948,8 +4168,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3992,8 +4213,11 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4036,8 +4260,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4080,52 +4307,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>300</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-2500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1000</v>
-      </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-97400</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-9000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4142,8 +4375,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4186,8 +4420,11 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4230,8 +4467,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4274,8 +4514,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4318,67 +4561,73 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E100" s="3">
         <v>170000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1900</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-60100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>303400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>11000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>16000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4406,40 +4655,43 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E102" s="3">
         <v>169700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20100</v>
       </c>
-      <c r="G102" s="3">
-        <v>-11000</v>
-      </c>
       <c r="H102" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-51100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>174100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-10000</v>
       </c>
       <c r="L102" s="3">
         <v>-10000</v>
       </c>
       <c r="M102" s="3">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -4448,6 +4700,9 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>
